--- a/docs/StructureDefinition-BRImunobiologicoAdministradoCampanha-2.0.xlsx
+++ b/docs/StructureDefinition-BRImunobiologicoAdministradoCampanha-2.0.xlsx
@@ -374,7 +374,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -598,7 +598,7 @@
     <t>The reason why a vaccine was not administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -910,7 +910,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -988,7 +988,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1073,7 +1073,7 @@
     <t>Immunization.patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1113,7 +1113,7 @@
     <t>Immunization.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1217,7 +1217,7 @@
     <t>The source of the data for a record which is not from a primary source.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-origin</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-origin|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=INF].role[classCode=PAT] (this syntax for self-reported) .participation[typeCode=INF].role[classCode=LIC] (this syntax for health care professional) .participation[typeCode=INF].role[classCode=PRS] (this syntax for family member)</t>
@@ -1226,7 +1226,7 @@
     <t>Immunization.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1411,7 +1411,7 @@
     <t>The site at which the vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-site|4.0.1</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1468,7 +1468,7 @@
     <t>The route by which the vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-route|4.0.1</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1516,7 +1516,7 @@
     <t>Immunization.doseQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1589,7 +1589,7 @@
     <t>The role a practitioner or organization plays in the immunization event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-function</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1705,7 +1705,7 @@
     <t>The reason why a vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1717,7 +1717,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1757,7 +1757,7 @@
     <t>The reason why a dose is considered to be subpotent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason|4.0.1</t>
   </si>
   <si>
     <t>Immunization.education</t>
@@ -1839,7 +1839,7 @@
     <t>The patient's eligibility for a vaccation program.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility|4.0.1</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 64994-7</t>
@@ -1857,7 +1857,7 @@
     <t>The source of funding used to purchase the vaccine administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source|4.0.1</t>
   </si>
   <si>
     <t>Immunization.reaction</t>
@@ -1902,7 +1902,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1981,7 +1981,7 @@
     <t>The vaccine preventable disease the dose is being administered for.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
@@ -2501,7 +2501,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>189</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>266</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>361</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>398</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>408</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>424</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>428</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>436</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>448</v>
       </c>
@@ -12666,7 +12666,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>467</v>
       </c>
@@ -14187,7 +14187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>492</v>
       </c>
@@ -16059,7 +16059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>524</v>
       </c>
@@ -19424,7 +19424,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>623</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
         <v>640</v>
       </c>
@@ -20471,12 +20471,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO155">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
